--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED14.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED14.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:53+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>339.55W</t>
+          <t>186W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L7"/>
+  <dimension ref="B2:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0074</t>
+          <t>SIM_XA_FIXED-2-0165</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>149W</t>
+          <t>30W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0季</t>
+          <t>3季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1749,171 +1749,6 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>第3年1季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-3-0037</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>4</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>167W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第3年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>4季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>4季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第3年4季</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0134</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>64W</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>1季</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>第4年3季</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0206</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>80W</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>3季</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
         </is>
       </c>
     </row>
@@ -1931,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G60"/>
+  <dimension ref="B2:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2251,10 +2086,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-12</v>
+        <v>-4</v>
       </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2263,7 +2098,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2280,7 +2115,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2299,14 +2134,14 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Auction_Win</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-14</v>
+        <v>-10</v>
       </c>
       <c r="E16" t="n">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2315,7 +2150,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>auction_bid_fee | {"order_id": "SIM_XA_FIXED-2-0165"}</t>
         </is>
       </c>
     </row>
@@ -2325,23 +2160,23 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>-48</v>
+        <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>404</v>
+        <v>450</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>第2年3季</t>
+          <t>第2年2季</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2351,14 +2186,14 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>-32</v>
+        <v>-12</v>
       </c>
       <c r="E18" t="n">
-        <v>372</v>
+        <v>438</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2367,7 +2202,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-8dc529cf12", "line_id": "L-ca714bcd86", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2377,14 +2212,14 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E19" t="n">
-        <v>358</v>
+        <v>430</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2393,7 +2228,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-8dc529cf12", "line_id": "L-ca714bcd86", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2410,11 +2245,11 @@
         <v>-14</v>
       </c>
       <c r="E20" t="n">
-        <v>344</v>
+        <v>416</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>第2年4季</t>
+          <t>第2年3季</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2429,14 +2264,14 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E21" t="n">
-        <v>329</v>
+        <v>402</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2445,7 +2280,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2455,14 +2290,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E22" t="n">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2471,7 +2306,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
+          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2323,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2497,7 +2332,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca714bcd86", "asset_type": "production_line"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2507,23 +2342,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
-        <v>478</v>
+        <v>387</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第2年4季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0074", "receivable_term_quarters": 0, "revenue_wan": 149.0}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca714bcd86", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2533,14 +2368,14 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>430</v>
+        <v>387</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -2549,7 +2384,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-2-0165", "receivable_term_quarters": 3, "revenue_wan": 30.0}</t>
         </is>
       </c>
     </row>
@@ -2559,14 +2394,14 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>-32</v>
+        <v>-12</v>
       </c>
       <c r="E26" t="n">
-        <v>398</v>
+        <v>375</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2575,7 +2410,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-5a51cc2255", "line_id": "L-ca714bcd86", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2585,14 +2420,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E27" t="n">
-        <v>386</v>
+        <v>367</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2601,7 +2436,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-5a51cc2255", "line_id": "L-ca714bcd86", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2611,14 +2446,14 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-14</v>
+        <v>-4</v>
       </c>
       <c r="E28" t="n">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2627,7 +2462,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2644,11 +2479,11 @@
         <v>-14</v>
       </c>
       <c r="E29" t="n">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年2季</t>
+          <t>第3年1季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2670,11 +2505,11 @@
         <v>-14</v>
       </c>
       <c r="E30" t="n">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2689,23 +2524,23 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>344</v>
+        <v>321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-3-0037", "receivable_term_quarters": 4, "revenue_wan": 167.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2715,23 +2550,23 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>-48</v>
+        <v>30</v>
       </c>
       <c r="E32" t="n">
-        <v>296</v>
+        <v>351</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第3年3季</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>receivable_collected | {"receivable_id": "AR-cf3a24d5fc"}</t>
         </is>
       </c>
     </row>
@@ -2741,14 +2576,14 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E33" t="n">
-        <v>264</v>
+        <v>337</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2757,7 +2592,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-330ab83fdf", "line_id": "L-ca714bcd86", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2767,14 +2602,14 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>-14</v>
+        <v>-15</v>
       </c>
       <c r="E34" t="n">
-        <v>250</v>
+        <v>322</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2783,7 +2618,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
         </is>
       </c>
     </row>
@@ -2793,14 +2628,14 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2809,7 +2644,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2661,7 @@
         <v>0</v>
       </c>
       <c r="E36" t="n">
-        <v>235</v>
+        <v>322</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2835,7 +2670,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca714bcd86", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -2845,23 +2680,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>0</v>
+        <v>-4</v>
       </c>
       <c r="E37" t="n">
-        <v>235</v>
+        <v>318</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca714bcd86", "asset_type": "production_line"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2871,23 +2706,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>income_tax_expense</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>-14.45</v>
+        <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>220.55</v>
+        <v>304</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>第3年4季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>income_tax_expense | {"pretax_income_wan": 57.8}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2897,23 +2732,23 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>208.55</v>
+        <v>290</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年2季</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2930,11 +2765,11 @@
         <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>194.55</v>
+        <v>276</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>第4年1季</t>
+          <t>第4年3季</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2956,11 +2791,11 @@
         <v>-14</v>
       </c>
       <c r="E41" t="n">
-        <v>180.55</v>
+        <v>262</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2975,23 +2810,23 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E42" t="n">
-        <v>180.55</v>
+        <v>247</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0134", "receivable_term_quarters": 1, "revenue_wan": 64.0}</t>
+          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
         </is>
       </c>
     </row>
@@ -3001,23 +2836,23 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>166.55</v>
+        <v>247</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3027,23 +2862,23 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
-        <v>333.55</v>
+        <v>247</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第4年4季</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-94a7537158"}</t>
+          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca714bcd86", "asset_type": "production_line"}</t>
         </is>
       </c>
     </row>
@@ -3053,23 +2888,23 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>64</v>
+        <v>-4</v>
       </c>
       <c r="E45" t="n">
-        <v>397.55</v>
+        <v>243</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>第4年3季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-7d6dab23fc"}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -3086,11 +2921,11 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>383.55</v>
+        <v>229</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年1季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3105,23 +2940,23 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>-15</v>
+        <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>368.55</v>
+        <v>215</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3131,23 +2966,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E48" t="n">
-        <v>368.55</v>
+        <v>201</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -3157,23 +2992,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Depreciation</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>-15</v>
       </c>
       <c r="E49" t="n">
-        <v>368.55</v>
+        <v>186</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第4年4季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca714bcd86", "asset_type": "production_line"}</t>
+          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
         </is>
       </c>
     </row>
@@ -3183,23 +3018,23 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>368.55</v>
+        <v>186</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0206", "receivable_term_quarters": 3, "revenue_wan": 80.0}</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3209,255 +3044,21 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>-24</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
-        <v>344.55</v>
+        <v>186</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
-        <is>
-          <t>emergency_material_purchase | {"cost_wan": 24.0, "material_id": "R1", "quantity": 2.0}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Product_Produce</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>-16</v>
-      </c>
-      <c r="E52" t="n">
-        <v>328.55</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 40.0, "job_id": "JOB-bba0501d67", "line_id": "L-ca714bcd86", "product_id": "P1", "quantity": 2.0, "remaining_quarters": 0}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="B53" t="n">
-        <v>50</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Pay_AD</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>-12</v>
-      </c>
-      <c r="E53" t="n">
-        <v>316.55</v>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="B54" t="n">
-        <v>51</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E54" t="n">
-        <v>302.55</v>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="B55" t="n">
-        <v>52</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E55" t="n">
-        <v>288.55</v>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>第5年2季</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="B56" t="n">
-        <v>53</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Pay_Overhaul</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>-14</v>
-      </c>
-      <c r="E56" t="n">
-        <v>274.55</v>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>management_fee_expense</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="B57" t="n">
-        <v>54</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Update_Receivable</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>80</v>
-      </c>
-      <c r="E57" t="n">
-        <v>354.55</v>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>第5年3季</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>receivable_collected | {"receivable_id": "AR-a05093878b"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="B58" t="n">
-        <v>55</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Pay_Maintenance</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>-15</v>
-      </c>
-      <c r="E58" t="n">
-        <v>339.55</v>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-ca714bcd86"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="B59" t="n">
-        <v>56</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" t="n">
-        <v>339.55</v>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-ca714bcd86", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="B60" t="n">
-        <v>57</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D60" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" t="n">
-        <v>339.55</v>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-ca714bcd86", "asset_type": "production_line"}</t>
         </is>
@@ -3564,16 +3165,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5">
@@ -3789,16 +3390,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="15">
@@ -3854,13 +3455,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>316</v>
+        <v>30</v>
       </c>
       <c r="G16" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3879,13 +3480,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>160</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3904,13 +3505,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>156</v>
+        <v>10</v>
       </c>
       <c r="G18" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3926,16 +3527,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
     </row>
     <row r="20">
@@ -3951,16 +3552,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-83</v>
+        <v>-75</v>
       </c>
       <c r="F20" t="n">
-        <v>73</v>
+        <v>-65</v>
       </c>
       <c r="G20" t="n">
-        <v>-59</v>
+        <v>-75</v>
       </c>
       <c r="H20" t="n">
-        <v>-29</v>
+        <v>-61</v>
       </c>
     </row>
     <row r="21">
@@ -4001,16 +3602,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-98.2</v>
+        <v>-90.2</v>
       </c>
       <c r="F22" t="n">
-        <v>57.8</v>
+        <v>-80.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-74.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-44.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="23">
@@ -4051,16 +3652,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-98.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F24" t="n">
-        <v>57.8</v>
+        <v>-80.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-74.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-44.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="25">
@@ -4079,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>14.45</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -4101,16 +3702,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-98.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F26" t="n">
-        <v>43.35</v>
+        <v>-80.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-74.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-44.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="28">
@@ -4200,16 +3801,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>329</v>
+        <v>387</v>
       </c>
       <c r="F30" t="n">
-        <v>220.55</v>
+        <v>322</v>
       </c>
       <c r="G30" t="n">
-        <v>368.55</v>
+        <v>247</v>
       </c>
       <c r="H30" t="n">
-        <v>339.55</v>
+        <v>186</v>
       </c>
     </row>
     <row r="31">
@@ -4228,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -4253,7 +3854,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -4275,16 +3876,16 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G33" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -4325,16 +3926,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F35" t="n">
-        <v>467.55</v>
+        <v>342</v>
       </c>
       <c r="G35" t="n">
-        <v>408.55</v>
+        <v>267</v>
       </c>
       <c r="H35" t="n">
-        <v>379.55</v>
+        <v>206</v>
       </c>
     </row>
     <row r="36">
@@ -4450,16 +4051,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>490.6</v>
+        <v>488.6</v>
       </c>
       <c r="F40" t="n">
-        <v>533.95</v>
+        <v>408.4</v>
       </c>
       <c r="G40" t="n">
-        <v>459.75</v>
+        <v>318.2</v>
       </c>
       <c r="H40" t="n">
-        <v>415.55</v>
+        <v>242</v>
       </c>
     </row>
     <row r="41">
@@ -4628,13 +4229,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-184.4000000000002</v>
+        <v>-186.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-141.0500000000002</v>
+        <v>-266.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-215.2500000000002</v>
+        <v>-356.8</v>
       </c>
     </row>
     <row r="48">
@@ -4650,16 +4251,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-98.2</v>
+        <v>-100.2</v>
       </c>
       <c r="F48" t="n">
-        <v>43.35</v>
+        <v>-80.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-74.2</v>
+        <v>-90.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-44.2</v>
+        <v>-76.2</v>
       </c>
     </row>
     <row r="49">
@@ -4675,16 +4276,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>490.6</v>
+        <v>488.6</v>
       </c>
       <c r="F49" t="n">
-        <v>533.9499999999998</v>
+        <v>408.4</v>
       </c>
       <c r="G49" t="n">
-        <v>459.7499999999998</v>
+        <v>318.2</v>
       </c>
       <c r="H49" t="n">
-        <v>415.5499999999998</v>
+        <v>242</v>
       </c>
     </row>
     <row r="50">
@@ -4700,16 +4301,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>490.6</v>
+        <v>488.6</v>
       </c>
       <c r="F50" t="n">
-        <v>533.9499999999998</v>
+        <v>408.4</v>
       </c>
       <c r="G50" t="n">
-        <v>459.7499999999998</v>
+        <v>318.2</v>
       </c>
       <c r="H50" t="n">
-        <v>415.5499999999998</v>
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -4780,7 +4381,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4929,7 +4530,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -5078,7 +4679,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -5227,7 +4828,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5376,7 +4977,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>16</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
